--- a/Result/profitability/8410.xlsx
+++ b/Result/profitability/8410.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM69"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>4.49</v>
       </c>
       <c r="M2" t="n">
-        <v>1.46</v>
+        <v>1.4025</v>
       </c>
       <c r="N2" t="n">
-        <v>36.47</v>
+        <v>35.46375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>4.62</v>
       </c>
       <c r="M3" t="n">
-        <v>1.92375</v>
+        <v>1.675</v>
       </c>
       <c r="N3" t="n">
-        <v>37.36624999999999</v>
+        <v>36.6075</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.65</v>
       </c>
       <c r="M4" t="n">
-        <v>1.825</v>
+        <v>1.7425</v>
       </c>
       <c r="N4" t="n">
-        <v>37.0025</v>
+        <v>36.67625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,16 +1018,16 @@
         <v>1.7</v>
       </c>
       <c r="M5" t="n">
-        <v>1.89875</v>
+        <v>2.105</v>
       </c>
       <c r="N5" t="n">
-        <v>36.65875</v>
+        <v>35.95</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>99.09999999999999</v>
@@ -1137,10 +1137,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>2.16625</v>
+        <v>2.01875</v>
       </c>
       <c r="N6" t="n">
-        <v>35.90375</v>
+        <v>36.08499999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.62</v>
       </c>
       <c r="M7" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="N7" t="n">
-        <v>35.78375</v>
+        <v>35.48</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.73</v>
       </c>
       <c r="M8" t="n">
-        <v>1.915</v>
+        <v>1.9</v>
       </c>
       <c r="N8" t="n">
-        <v>36.0225</v>
+        <v>36.17125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9191,6 +9191,133 @@
       </c>
       <c r="AM69" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>8410</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>239</v>
+      </c>
+      <c r="D70" t="n">
+        <v>161</v>
+      </c>
+      <c r="E70" t="n">
+        <v>78</v>
+      </c>
+      <c r="F70" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="G70" t="n">
+        <v>17</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>7.08%</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>4</v>
+      </c>
+      <c r="J70" t="n">
+        <v>21</v>
+      </c>
+      <c r="K70" t="n">
+        <v>17</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="N70" t="n">
+        <v>35.27375</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W70" t="n">
+        <v>-0.1199999999999999</v>
+      </c>
+      <c r="X70" t="n">
+        <v>-0.2105263157894736</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>1.190000000000001</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.03800702650910259</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>-1.375</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>-5.670000000000002</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>-0.1485459785171601</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
